--- a/table/Datas/__enums__.xlsx
+++ b/table/Datas/__enums__.xlsx
@@ -413,13 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unique</t>
         </is>
       </c>
     </row>
